--- a/주파수계산.xlsx
+++ b/주파수계산.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\ai_algorithm_create\Crain_testbed\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dustin08/Documents/Github/PHM_Solutions_Crane_Mock_Test/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33EE5F12-0711-464B-B90F-A0D6AC3BA010}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35351C58-3B94-5F47-BB38-23547CB66478}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="51600" yWindow="3750" windowWidth="21810" windowHeight="17550" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="구동계_진동_계산기" sheetId="1" r:id="rId1"/>
@@ -108,9 +108,6 @@
     <t>베어링 모델/명칭</t>
   </si>
   <si>
-    <t>6208 (예시)</t>
-  </si>
-  <si>
     <t>볼/롤러 직경 (d)</t>
   </si>
   <si>
@@ -209,6 +206,10 @@
   </si>
   <si>
     <t>설정 RPM (Input)</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>NTN N306E</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -229,7 +230,7 @@
     <numFmt numFmtId="185" formatCode="0.00\ &quot;mm&quot;"/>
     <numFmt numFmtId="186" formatCode="0.0\ &quot;deg&quot;"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1228,7 +1229,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G29"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -1237,7 +1238,7 @@
     <col min="7" max="7" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -1248,7 +1249,7 @@
       <c r="F1" s="22"/>
       <c r="G1" s="22"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7">
       <c r="A2" s="22"/>
       <c r="B2" s="22"/>
       <c r="C2" s="22"/>
@@ -1257,7 +1258,7 @@
       <c r="F2" s="22"/>
       <c r="G2" s="22"/>
     </row>
-    <row r="4" spans="1:7" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="18">
       <c r="A4" s="21" t="s">
         <v>1</v>
       </c>
@@ -1268,22 +1269,22 @@
       <c r="F4" s="22"/>
       <c r="G4" s="22"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7">
       <c r="A5" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B5" s="2">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E5" s="4">
         <f>B$5*120/4</f>
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7" s="5" t="s">
         <v>3</v>
       </c>
@@ -1300,34 +1301,34 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7">
       <c r="A8" s="6" t="s">
         <v>8</v>
       </c>
       <c r="B8" s="7">
         <f>E$5</f>
-        <v>1200</v>
+        <v>2100</v>
       </c>
       <c r="C8" s="8">
         <f>B8/60</f>
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="D8" s="9"/>
       <c r="E8" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7">
       <c r="A9" s="6" t="s">
         <v>10</v>
       </c>
       <c r="B9" s="7">
         <f>B$8*D$9</f>
-        <v>699.96</v>
+        <v>1224.93</v>
       </c>
       <c r="C9" s="8">
         <f>B9/60</f>
-        <v>11.666</v>
+        <v>20.415500000000002</v>
       </c>
       <c r="D9">
         <v>0.58330000000000004</v>
@@ -1336,17 +1337,17 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7">
       <c r="A10" s="6" t="s">
         <v>12</v>
       </c>
       <c r="B10" s="7">
         <f>B$9*D$10</f>
-        <v>69.996000000000009</v>
+        <v>122.49300000000001</v>
       </c>
       <c r="C10" s="8">
         <f>B10/60</f>
-        <v>1.1666000000000001</v>
+        <v>2.04155</v>
       </c>
       <c r="D10">
         <v>0.1</v>
@@ -1355,7 +1356,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="18">
       <c r="A12" s="21" t="s">
         <v>14</v>
       </c>
@@ -1366,7 +1367,7 @@
       <c r="F12" s="22"/>
       <c r="G12" s="22"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7">
       <c r="A13" s="10" t="s">
         <v>15</v>
       </c>
@@ -1374,7 +1375,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7">
       <c r="A15" s="5" t="s">
         <v>16</v>
       </c>
@@ -1391,27 +1392,27 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7">
       <c r="A16" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B16" s="7">
         <f>B10</f>
-        <v>69.996000000000009</v>
+        <v>122.49300000000001</v>
       </c>
       <c r="C16" s="8">
         <f>C10</f>
-        <v>1.1666000000000001</v>
+        <v>2.04155</v>
       </c>
       <c r="D16" s="8">
         <f>C16*$B$13</f>
-        <v>20.998800000000003</v>
+        <v>36.747900000000001</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7">
       <c r="A17" s="6"/>
       <c r="B17" s="7"/>
       <c r="C17" s="8"/>
@@ -1419,7 +1420,7 @@
       <c r="E17" s="12"/>
       <c r="F17" s="6"/>
     </row>
-    <row r="20" spans="1:7" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="18">
       <c r="A20" s="21" t="s">
         <v>22</v>
       </c>
@@ -1430,153 +1431,153 @@
       <c r="F20" s="22"/>
       <c r="G20" s="22"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7">
       <c r="A21" s="10" t="s">
         <v>23</v>
       </c>
       <c r="B21" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="D21" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="D21" s="10" t="s">
+      <c r="E21" s="14">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="E21" s="14">
+      <c r="B22" s="15">
         <v>12</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" s="10" t="s">
+      <c r="D22" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="B22" s="15">
-        <v>9</v>
-      </c>
-      <c r="D22" s="10" t="s">
+      <c r="E22" s="14">
+        <v>51.5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" s="10" t="s">
         <v>27</v>
-      </c>
-      <c r="E22" s="14">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="10" t="s">
-        <v>28</v>
       </c>
       <c r="B23" s="16">
         <v>0</v>
       </c>
       <c r="D23" s="10"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7">
       <c r="A25" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B25" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="C25" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C25" s="5" t="s">
+      <c r="D25" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="D25" s="5" t="s">
+      <c r="E25" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="E25" s="5" t="s">
+      <c r="F25" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="F25" s="5" t="s">
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" s="6" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26" s="6" t="s">
+      <c r="B26" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="B26" s="17" t="s">
+      <c r="C26" s="6" t="s">
         <v>36</v>
-      </c>
-      <c r="C26" s="6" t="s">
-        <v>37</v>
       </c>
       <c r="D26" s="8">
         <f>( $B$22 / 2 ) * C8 * ( 1 - ( $E$21 / $E$22 ) * COS(RADIANS($B$23)) )</f>
-        <v>72</v>
+        <v>165.14563106796115</v>
       </c>
       <c r="E26" s="8">
         <f>( $B$22 / 2 ) * C9 * ( 1 - ( $E$21 / $E$22 ) * COS(RADIANS($B$23)) )</f>
-        <v>41.997600000000006</v>
+        <v>96.329446601941754</v>
       </c>
       <c r="F26" s="8">
         <f>( $B$22 / 2 ) * C10 * ( 1 - ( $E$21 / $E$22 ) * COS(RADIANS($B$23)) )</f>
-        <v>4.1997600000000004</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+        <v>9.6329446601941751</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
       <c r="A27" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B27" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="B27" s="17" t="s">
+      <c r="C27" s="6" t="s">
         <v>39</v>
-      </c>
-      <c r="C27" s="6" t="s">
-        <v>40</v>
       </c>
       <c r="D27" s="8">
         <f>( $B$22 / 2 ) * C8 * ( 1 + ( $E$21 / $E$22 ) * COS(RADIANS($B$23)) )</f>
-        <v>108</v>
+        <v>254.85436893203882</v>
       </c>
       <c r="E27" s="8">
         <f>( $B$22 / 2 ) * C9 * ( 1 + ( $E$21 / $E$22 ) * COS(RADIANS($B$23)) )</f>
-        <v>62.996399999999994</v>
+        <v>148.65655339805826</v>
       </c>
       <c r="F27" s="8">
         <f>( $B$22 / 2 ) * C10 * ( 1 + ( $E$21 / $E$22 ) * COS(RADIANS($B$23)) )</f>
-        <v>6.299640000000001</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+        <v>14.865655339805825</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
       <c r="A28" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B28" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="B28" s="17" t="s">
+      <c r="C28" s="6" t="s">
         <v>42</v>
-      </c>
-      <c r="C28" s="6" t="s">
-        <v>43</v>
       </c>
       <c r="D28" s="8">
         <f>( $E$22 / (2 * $E$21) ) * C8 * ( 1 - ( ($E$21 / $E$22) * COS(RADIANS($B$23)) )^2 )</f>
-        <v>48</v>
+        <v>78.193954104148261</v>
       </c>
       <c r="E28" s="8">
         <f>( $E$22 / (2 * $E$21) ) * C9 * ( 1 - ( ($E$21 / $E$22) * COS(RADIANS($B$23)) )^2 )</f>
-        <v>27.998399999999997</v>
+        <v>45.610533428949694</v>
       </c>
       <c r="F28" s="8">
         <f>( $E$22 / (2 * $E$21) ) * C10 * ( 1 - ( ($E$21 / $E$22) * COS(RADIANS($B$23)) )^2 )</f>
-        <v>2.7998400000000001</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+        <v>4.5610533428949687</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
       <c r="A29" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B29" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="B29" s="17" t="s">
+      <c r="C29" s="6" t="s">
         <v>45</v>
-      </c>
-      <c r="C29" s="6" t="s">
-        <v>46</v>
       </c>
       <c r="D29" s="8">
         <f>( 1 / 2 ) * C8 * ( 1 - ( $E$21 / $E$22 ) * COS(RADIANS($B$23)) )</f>
-        <v>8</v>
+        <v>13.762135922330097</v>
       </c>
       <c r="E29" s="8">
         <f>( 1 / 2 ) * C9 * ( 1 - ( $E$21 / $E$22 ) * COS(RADIANS($B$23)) )</f>
-        <v>4.6664000000000003</v>
+        <v>8.0274538834951468</v>
       </c>
       <c r="F29" s="8">
         <f>( 1 / 2 ) * C10 * ( 1 - ( $E$21 / $E$22 ) * COS(RADIANS($B$23)) )</f>
-        <v>0.46664000000000005</v>
+        <v>0.80274538834951459</v>
       </c>
     </row>
   </sheetData>
@@ -1594,14 +1595,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F15"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
     <col min="1" max="6" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6">
       <c r="A1" s="23" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B1" s="22"/>
       <c r="C1" s="22"/>
@@ -1609,7 +1610,7 @@
       <c r="E1" s="22"/>
       <c r="F1" s="22"/>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6">
       <c r="A2" s="22"/>
       <c r="B2" s="22"/>
       <c r="C2" s="22"/>
@@ -1617,27 +1618,27 @@
       <c r="E2" s="22"/>
       <c r="F2" s="22"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6">
       <c r="A4" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="C4" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="D4" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="E4" s="5" t="s">
         <v>51</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>52</v>
       </c>
       <c r="F4" s="5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6">
       <c r="A5" s="18">
         <v>10</v>
       </c>
@@ -1658,10 +1659,10 @@
         <v>5.25</v>
       </c>
       <c r="F5" s="17" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6" s="18">
         <v>15</v>
       </c>
@@ -1682,10 +1683,10 @@
         <v>7.875</v>
       </c>
       <c r="F6" s="17" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7" s="18">
         <v>20</v>
       </c>
@@ -1706,10 +1707,10 @@
         <v>10.5</v>
       </c>
       <c r="F7" s="17" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8" s="18">
         <v>25</v>
       </c>
@@ -1730,10 +1731,10 @@
         <v>13.125</v>
       </c>
       <c r="F8" s="17" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9" s="18">
         <v>30</v>
       </c>
@@ -1754,10 +1755,10 @@
         <v>15.75</v>
       </c>
       <c r="F9" s="17" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10" s="18">
         <v>35</v>
       </c>
@@ -1778,10 +1779,10 @@
         <v>18.375</v>
       </c>
       <c r="F10" s="17" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
       <c r="A11" s="18">
         <v>40</v>
       </c>
@@ -1802,10 +1803,10 @@
         <v>21</v>
       </c>
       <c r="F11" s="17" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
       <c r="A12" s="18">
         <v>45</v>
       </c>
@@ -1826,10 +1827,10 @@
         <v>23.625</v>
       </c>
       <c r="F12" s="17" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
       <c r="A13" s="18">
         <v>50</v>
       </c>
@@ -1850,10 +1851,10 @@
         <v>26.25</v>
       </c>
       <c r="F13" s="17" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
       <c r="A14" s="18">
         <v>55</v>
       </c>
@@ -1874,10 +1875,10 @@
         <v>28.875</v>
       </c>
       <c r="F14" s="17" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
       <c r="A15" s="18">
         <v>60</v>
       </c>
@@ -1898,7 +1899,7 @@
         <v>31.5</v>
       </c>
       <c r="F15" s="17" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>

--- a/주파수계산.xlsx
+++ b/주파수계산.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dustin08/Documents/Github/PHM_Solutions_Crane_Mock_Test/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35351C58-3B94-5F47-BB38-23547CB66478}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3050F8C-892C-774B-85E6-2075FFF520E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="17280" yWindow="660" windowWidth="17280" windowHeight="20440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="구동계_진동_계산기" sheetId="1" r:id="rId1"/>
@@ -1274,14 +1274,14 @@
         <v>2</v>
       </c>
       <c r="B5" s="2">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E5" s="4">
         <f>B$5*120/4</f>
-        <v>2100</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1307,11 +1307,11 @@
       </c>
       <c r="B8" s="7">
         <f>E$5</f>
-        <v>2100</v>
+        <v>1800</v>
       </c>
       <c r="C8" s="8">
         <f>B8/60</f>
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D8" s="9"/>
       <c r="E8" s="6" t="s">
@@ -1324,11 +1324,11 @@
       </c>
       <c r="B9" s="7">
         <f>B$8*D$9</f>
-        <v>1224.93</v>
+        <v>1049.94</v>
       </c>
       <c r="C9" s="8">
         <f>B9/60</f>
-        <v>20.415500000000002</v>
+        <v>17.499000000000002</v>
       </c>
       <c r="D9">
         <v>0.58330000000000004</v>
@@ -1343,11 +1343,11 @@
       </c>
       <c r="B10" s="7">
         <f>B$9*D$10</f>
-        <v>122.49300000000001</v>
+        <v>104.99400000000001</v>
       </c>
       <c r="C10" s="8">
         <f>B10/60</f>
-        <v>2.04155</v>
+        <v>1.7499000000000002</v>
       </c>
       <c r="D10">
         <v>0.1</v>
@@ -1398,15 +1398,15 @@
       </c>
       <c r="B16" s="7">
         <f>B10</f>
-        <v>122.49300000000001</v>
+        <v>104.99400000000001</v>
       </c>
       <c r="C16" s="8">
         <f>C10</f>
-        <v>2.04155</v>
+        <v>1.7499000000000002</v>
       </c>
       <c r="D16" s="8">
         <f>C16*$B$13</f>
-        <v>36.747900000000001</v>
+        <v>31.498200000000004</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>21</v>
@@ -1500,15 +1500,15 @@
       </c>
       <c r="D26" s="8">
         <f>( $B$22 / 2 ) * C8 * ( 1 - ( $E$21 / $E$22 ) * COS(RADIANS($B$23)) )</f>
-        <v>165.14563106796115</v>
+        <v>141.55339805825241</v>
       </c>
       <c r="E26" s="8">
         <f>( $B$22 / 2 ) * C9 * ( 1 - ( $E$21 / $E$22 ) * COS(RADIANS($B$23)) )</f>
-        <v>96.329446601941754</v>
+        <v>82.568097087378646</v>
       </c>
       <c r="F26" s="8">
         <f>( $B$22 / 2 ) * C10 * ( 1 - ( $E$21 / $E$22 ) * COS(RADIANS($B$23)) )</f>
-        <v>9.6329446601941751</v>
+        <v>8.2568097087378653</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1523,15 +1523,15 @@
       </c>
       <c r="D27" s="8">
         <f>( $B$22 / 2 ) * C8 * ( 1 + ( $E$21 / $E$22 ) * COS(RADIANS($B$23)) )</f>
-        <v>254.85436893203882</v>
+        <v>218.44660194174756</v>
       </c>
       <c r="E27" s="8">
         <f>( $B$22 / 2 ) * C9 * ( 1 + ( $E$21 / $E$22 ) * COS(RADIANS($B$23)) )</f>
-        <v>148.65655339805826</v>
+        <v>127.41990291262137</v>
       </c>
       <c r="F27" s="8">
         <f>( $B$22 / 2 ) * C10 * ( 1 + ( $E$21 / $E$22 ) * COS(RADIANS($B$23)) )</f>
-        <v>14.865655339805825</v>
+        <v>12.741990291262137</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1546,15 +1546,15 @@
       </c>
       <c r="D28" s="8">
         <f>( $E$22 / (2 * $E$21) ) * C8 * ( 1 - ( ($E$21 / $E$22) * COS(RADIANS($B$23)) )^2 )</f>
-        <v>78.193954104148261</v>
+        <v>67.023389232127087</v>
       </c>
       <c r="E28" s="8">
         <f>( $E$22 / (2 * $E$21) ) * C9 * ( 1 - ( ($E$21 / $E$22) * COS(RADIANS($B$23)) )^2 )</f>
-        <v>45.610533428949694</v>
+        <v>39.094742939099739</v>
       </c>
       <c r="F28" s="8">
         <f>( $E$22 / (2 * $E$21) ) * C10 * ( 1 - ( ($E$21 / $E$22) * COS(RADIANS($B$23)) )^2 )</f>
-        <v>4.5610533428949687</v>
+        <v>3.9094742939099736</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1569,15 +1569,15 @@
       </c>
       <c r="D29" s="8">
         <f>( 1 / 2 ) * C8 * ( 1 - ( $E$21 / $E$22 ) * COS(RADIANS($B$23)) )</f>
-        <v>13.762135922330097</v>
+        <v>11.796116504854369</v>
       </c>
       <c r="E29" s="8">
         <f>( 1 / 2 ) * C9 * ( 1 - ( $E$21 / $E$22 ) * COS(RADIANS($B$23)) )</f>
-        <v>8.0274538834951468</v>
+        <v>6.8806747572815539</v>
       </c>
       <c r="F29" s="8">
         <f>( 1 / 2 ) * C10 * ( 1 - ( $E$21 / $E$22 ) * COS(RADIANS($B$23)) )</f>
-        <v>0.80274538834951459</v>
+        <v>0.68806747572815541</v>
       </c>
     </row>
   </sheetData>

--- a/주파수계산.xlsx
+++ b/주파수계산.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dustin08/Documents/Github/PHM_Solutions_Crane_Mock_Test/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3050F8C-892C-774B-85E6-2075FFF520E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0AEF6E5-554D-9A44-A168-A78E3621680D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17280" yWindow="660" windowWidth="17280" windowHeight="20440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20" yWindow="680" windowWidth="34560" windowHeight="20440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="구동계_진동_계산기" sheetId="1" r:id="rId1"/>
@@ -1274,14 +1274,14 @@
         <v>2</v>
       </c>
       <c r="B5" s="2">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E5" s="4">
         <f>B$5*120/4</f>
-        <v>1800</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1307,11 +1307,11 @@
       </c>
       <c r="B8" s="7">
         <f>E$5</f>
-        <v>1800</v>
+        <v>2400</v>
       </c>
       <c r="C8" s="8">
         <f>B8/60</f>
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D8" s="9"/>
       <c r="E8" s="6" t="s">
@@ -1324,11 +1324,11 @@
       </c>
       <c r="B9" s="7">
         <f>B$8*D$9</f>
-        <v>1049.94</v>
+        <v>1399.92</v>
       </c>
       <c r="C9" s="8">
         <f>B9/60</f>
-        <v>17.499000000000002</v>
+        <v>23.332000000000001</v>
       </c>
       <c r="D9">
         <v>0.58330000000000004</v>
@@ -1343,11 +1343,11 @@
       </c>
       <c r="B10" s="7">
         <f>B$9*D$10</f>
-        <v>104.99400000000001</v>
+        <v>139.99200000000002</v>
       </c>
       <c r="C10" s="8">
         <f>B10/60</f>
-        <v>1.7499000000000002</v>
+        <v>2.3332000000000002</v>
       </c>
       <c r="D10">
         <v>0.1</v>
@@ -1398,15 +1398,15 @@
       </c>
       <c r="B16" s="7">
         <f>B10</f>
-        <v>104.99400000000001</v>
+        <v>139.99200000000002</v>
       </c>
       <c r="C16" s="8">
         <f>C10</f>
-        <v>1.7499000000000002</v>
+        <v>2.3332000000000002</v>
       </c>
       <c r="D16" s="8">
         <f>C16*$B$13</f>
-        <v>31.498200000000004</v>
+        <v>41.997600000000006</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>21</v>
@@ -1500,15 +1500,15 @@
       </c>
       <c r="D26" s="8">
         <f>( $B$22 / 2 ) * C8 * ( 1 - ( $E$21 / $E$22 ) * COS(RADIANS($B$23)) )</f>
-        <v>141.55339805825241</v>
+        <v>188.73786407766991</v>
       </c>
       <c r="E26" s="8">
         <f>( $B$22 / 2 ) * C9 * ( 1 - ( $E$21 / $E$22 ) * COS(RADIANS($B$23)) )</f>
-        <v>82.568097087378646</v>
+        <v>110.09079611650486</v>
       </c>
       <c r="F26" s="8">
         <f>( $B$22 / 2 ) * C10 * ( 1 - ( $E$21 / $E$22 ) * COS(RADIANS($B$23)) )</f>
-        <v>8.2568097087378653</v>
+        <v>11.009079611650487</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1523,15 +1523,15 @@
       </c>
       <c r="D27" s="8">
         <f>( $B$22 / 2 ) * C8 * ( 1 + ( $E$21 / $E$22 ) * COS(RADIANS($B$23)) )</f>
-        <v>218.44660194174756</v>
+        <v>291.26213592233006</v>
       </c>
       <c r="E27" s="8">
         <f>( $B$22 / 2 ) * C9 * ( 1 + ( $E$21 / $E$22 ) * COS(RADIANS($B$23)) )</f>
-        <v>127.41990291262137</v>
+        <v>169.89320388349515</v>
       </c>
       <c r="F27" s="8">
         <f>( $B$22 / 2 ) * C10 * ( 1 + ( $E$21 / $E$22 ) * COS(RADIANS($B$23)) )</f>
-        <v>12.741990291262137</v>
+        <v>16.989320388349515</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1546,15 +1546,15 @@
       </c>
       <c r="D28" s="8">
         <f>( $E$22 / (2 * $E$21) ) * C8 * ( 1 - ( ($E$21 / $E$22) * COS(RADIANS($B$23)) )^2 )</f>
-        <v>67.023389232127087</v>
+        <v>89.36451897616945</v>
       </c>
       <c r="E28" s="8">
         <f>( $E$22 / (2 * $E$21) ) * C9 * ( 1 - ( ($E$21 / $E$22) * COS(RADIANS($B$23)) )^2 )</f>
-        <v>39.094742939099739</v>
+        <v>52.126323918799649</v>
       </c>
       <c r="F28" s="8">
         <f>( $E$22 / (2 * $E$21) ) * C10 * ( 1 - ( ($E$21 / $E$22) * COS(RADIANS($B$23)) )^2 )</f>
-        <v>3.9094742939099736</v>
+        <v>5.2126323918799651</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1569,15 +1569,15 @@
       </c>
       <c r="D29" s="8">
         <f>( 1 / 2 ) * C8 * ( 1 - ( $E$21 / $E$22 ) * COS(RADIANS($B$23)) )</f>
-        <v>11.796116504854369</v>
+        <v>15.728155339805825</v>
       </c>
       <c r="E29" s="8">
         <f>( 1 / 2 ) * C9 * ( 1 - ( $E$21 / $E$22 ) * COS(RADIANS($B$23)) )</f>
-        <v>6.8806747572815539</v>
+        <v>9.1742330097087379</v>
       </c>
       <c r="F29" s="8">
         <f>( 1 / 2 ) * C10 * ( 1 - ( $E$21 / $E$22 ) * COS(RADIANS($B$23)) )</f>
-        <v>0.68806747572815541</v>
+        <v>0.91742330097087388</v>
       </c>
     </row>
   </sheetData>
